--- a/ingestion/tests/fixtures/xlsx/rcpa_tiny.xlsx
+++ b/ingestion/tests/fixtures/xlsx/rcpa_tiny.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RCPA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RCPA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/ingestion/tests/fixtures/xlsx/rcpa_tiny.xlsx
+++ b/ingestion/tests/fixtures/xlsx/rcpa_tiny.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,20 +439,45 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Speciality</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Patch</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Active Status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SKU Detail</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>O &amp; C</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -479,18 +504,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Colombo 1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Cipla Brand</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SKU A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Own</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="n">
+      <c r="M2" t="n">
         <v>3100</v>
       </c>
     </row>
